--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,6 +907,230 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137219316</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137234347</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90925</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalasjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591648</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7162110</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137234347</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137234349</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79524</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalasjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591659</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7162158</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137234349</t>
         </is>
       </c>
     </row>
@@ -914,6 +1138,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52815-2025 artfynd.xlsx
+++ b/artfynd/A 52815-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137219252</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137219316</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137234347</v>
       </c>
       <c r="B4" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>137234349</v>
       </c>
       <c r="B5" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
